--- a/templates/CapacitySlotTemplate.xlsx
+++ b/templates/CapacitySlotTemplate.xlsx
@@ -1,38 +1,120 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\n.habibifar\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4D25541-E0E5-4815-8066-87DC8CA6D46C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+  <si>
+    <t>Hub Network ID</t>
+  </si>
+  <si>
+    <t>Hub Time Slot ID</t>
+  </si>
+  <si>
+    <t>Time Slot</t>
+  </si>
+  <si>
+    <t>Daily Capacity</t>
+  </si>
+  <si>
+    <t>Start date</t>
+  </si>
+  <si>
+    <t>End date</t>
+  </si>
+  <si>
+    <t>Saturday</t>
+  </si>
+  <si>
+    <t>Sunday</t>
+  </si>
+  <si>
+    <t>Monday</t>
+  </si>
+  <si>
+    <t>Tuesday</t>
+  </si>
+  <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
+    <t>Thursday</t>
+  </si>
+  <si>
+    <t>Friday</t>
+  </si>
+  <si>
+    <t>Volume Capacity</t>
+  </si>
+  <si>
+    <t>Weight Capacity</t>
+  </si>
+  <si>
+    <t>Shipping Size</t>
+  </si>
+  <si>
+    <t>Pickup Reservable</t>
+  </si>
+  <si>
+    <t>Delivery Reservable</t>
+  </si>
+  <si>
+    <t>Active For Drop Shipping</t>
+  </si>
+  <si>
+    <t>Drop Network ID</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>11 - 15</t>
+  </si>
+  <si>
+    <t>1404/03/01</t>
+  </si>
+  <si>
+    <t>1404/06/31</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -110,41 +192,52 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
-    <dxf>
-      <alignment horizontal="center" vertical="bottom"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom"/>
-      <border outline="0">
+  <dxfs count="26">
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -153,6 +246,25 @@
         </right>
         <top/>
         <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom"/>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -483,123 +595,81 @@
     </dxf>
     <dxf>
       <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom"/>
     </dxf>
     <dxf>
       <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom"/>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:S2" headerRowCount="1" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="22" tableBorderDxfId="23" totalsRowBorderDxfId="21">
-  <autoFilter ref="A1:S2"/>
-  <tableColumns count="19">
-    <tableColumn id="1" name="Hub Network ID" dataDxfId="20"/>
-    <tableColumn id="2" name="Hub Time Slot ID" dataDxfId="19"/>
-    <tableColumn id="3" name="Time Slot" dataDxfId="18"/>
-    <tableColumn id="4" name="Daily Capacity" dataDxfId="17"/>
-    <tableColumn id="5" name="Start date" dataDxfId="16"/>
-    <tableColumn id="6" name="End date" dataDxfId="15"/>
-    <tableColumn id="7" name="Saturday" dataDxfId="14"/>
-    <tableColumn id="8" name="Sunday" dataDxfId="13"/>
-    <tableColumn id="9" name="Monday" dataDxfId="12"/>
-    <tableColumn id="10" name="Tuesday" dataDxfId="11"/>
-    <tableColumn id="11" name="Wednesday" dataDxfId="10"/>
-    <tableColumn id="12" name="Thursday" dataDxfId="9"/>
-    <tableColumn id="13" name="Friday" dataDxfId="8"/>
-    <tableColumn id="14" name="Volume Capacity" dataDxfId="7"/>
-    <tableColumn id="15" name="Weight Capacity" dataDxfId="6"/>
-    <tableColumn id="16" name="Shipping Size" dataDxfId="5"/>
-    <tableColumn id="17" name="Pickup Reservable" dataDxfId="4"/>
-    <tableColumn id="18" name="Delivery Reservable" dataDxfId="3"/>
-    <tableColumn id="19" name="Active For Drop Shipping" dataDxfId="2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:U2" totalsRowShown="0" headerRowDxfId="25" dataDxfId="23" headerRowBorderDxfId="24" tableBorderDxfId="22" totalsRowBorderDxfId="21">
+  <autoFilter ref="A1:U2" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="21">
+    <tableColumn id="21" xr3:uid="{F2879594-76E7-4DCD-82F8-8728AA180320}" name="Active" dataDxfId="0"/>
+    <tableColumn id="20" xr3:uid="{AFF31FFE-0343-4560-AAB8-1C94748DCACF}" name="Drop Network ID" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Hub Network ID" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Hub Time Slot ID" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Time Slot" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Daily Capacity" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Start date" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="End date" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Saturday" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Sunday" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Monday" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Tuesday" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Wednesday" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Thursday" dataDxfId="9"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Friday" dataDxfId="8"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Volume Capacity" dataDxfId="7"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Weight Capacity" dataDxfId="6"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Shipping Size" dataDxfId="5"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Pickup Reservable" dataDxfId="4"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Delivery Reservable" dataDxfId="3"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Active For Drop Shipping" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -901,213 +971,161 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="17.140625" customWidth="1" min="1" max="1"/>
-    <col width="17.7109375" customWidth="1" min="2" max="2"/>
-    <col width="11.42578125" customWidth="1" min="3" max="3"/>
-    <col width="15.42578125" customWidth="1" min="4" max="4"/>
-    <col width="11.7109375" customWidth="1" min="5" max="5"/>
-    <col width="10.85546875" customWidth="1" min="6" max="7"/>
-    <col width="9.5703125" customWidth="1" min="8" max="8"/>
-    <col width="10.42578125" customWidth="1" min="9" max="10"/>
-    <col width="13.7109375" customWidth="1" min="11" max="11"/>
-    <col width="11.140625" customWidth="1" min="12" max="12"/>
-    <col width="8.5703125" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="17.5703125" customWidth="1" min="15" max="15"/>
-    <col width="14.85546875" customWidth="1" min="16" max="16"/>
-    <col width="19.28515625" customWidth="1" min="17" max="17"/>
-    <col width="20.85546875" customWidth="1" min="18" max="18"/>
-    <col width="24.85546875" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
+    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" customWidth="1"/>
+    <col min="6" max="7" width="10.85546875" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="10" width="10.42578125" customWidth="1"/>
+    <col min="11" max="11" width="13.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.140625" customWidth="1"/>
+    <col min="13" max="13" width="8.5703125" customWidth="1"/>
+    <col min="14" max="14" width="18" customWidth="1"/>
+    <col min="15" max="15" width="17.5703125" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" customWidth="1"/>
+    <col min="17" max="17" width="19.28515625" customWidth="1"/>
+    <col min="18" max="18" width="20.85546875" customWidth="1"/>
+    <col min="19" max="19" width="24.85546875" customWidth="1"/>
+    <col min="20" max="20" width="18" customWidth="1"/>
+    <col min="21" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Hub Network ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Hub Time Slot ID</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Time Slot</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Daily Capacity</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Start date</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>End date</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>Volume Capacity</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>Weight Capacity</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>Shipping Size</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>Pickup Reservable</t>
-        </is>
-      </c>
-      <c r="R1" s="2" t="inlineStr">
-        <is>
-          <t>Delivery Reservable</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>Active For Drop Shipping</t>
-        </is>
-      </c>
-      <c r="T1" s="3" t="inlineStr">
-        <is>
-          <t>Drop Network ID</t>
-        </is>
-      </c>
-      <c r="U1" s="3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="4" t="n">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4">
         <v>3673</v>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="D2" s="5">
         <v>2160</v>
       </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>11 - 15</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="n">
+      <c r="E2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="5">
         <v>5000</v>
       </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>1404/03/01</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>1404/06/31</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="n">
+      <c r="G2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="5">
         <v>1</v>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="J2" s="5">
         <v>1</v>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="K2" s="5">
         <v>1</v>
       </c>
-      <c r="J2" s="5" t="n">
+      <c r="L2" s="5">
         <v>1</v>
       </c>
-      <c r="K2" s="5" t="n">
+      <c r="M2" s="5">
         <v>1</v>
       </c>
-      <c r="L2" s="5" t="n">
+      <c r="N2" s="5">
         <v>1</v>
       </c>
-      <c r="M2" s="5" t="n"/>
-      <c r="N2" s="5" t="n">
+      <c r="O2" s="5"/>
+      <c r="P2" s="5">
         <v>4294967295</v>
       </c>
-      <c r="O2" s="5" t="n">
+      <c r="Q2" s="5">
         <v>4294967295</v>
       </c>
-      <c r="P2" s="5" t="n">
+      <c r="R2" s="5">
         <v>1</v>
       </c>
-      <c r="Q2" s="5" t="n">
+      <c r="S2" s="5">
         <v>1</v>
       </c>
-      <c r="R2" s="5" t="n"/>
-      <c r="S2" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T2" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" s="6" t="n">
+      <c r="T2" s="5"/>
+      <c r="U2" s="6">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>